--- a/attendance-mail/勤務時間管理.xlsx
+++ b/attendance-mail/勤務時間管理.xlsx
@@ -2741,7 +2741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2855,10 +2855,26 @@
           <t>CC</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>全員共通の CC（任意、; 区切り）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>送信後に打刻をクリア</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ON=送信できた行の出勤打刻時刻(C列)を自動で消す / OFF=残す</t>
         </is>
       </c>
     </row>
@@ -2893,9 +2909,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -2917,9 +2931,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -2927,9 +2939,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>

--- a/attendance-mail/勤務時間管理.xlsx
+++ b/attendance-mail/勤務時間管理.xlsx
@@ -511,10 +511,8 @@
           <t>taro@example.co.jp</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>7:45</t>
-        </is>
+      <c r="C2" s="3" t="n">
+        <v>0.3229166666666667</v>
       </c>
       <c r="D2" s="4">
         <f>IF(N(C2)=0,"",C2+TIME(13,0,0))</f>
@@ -534,10 +532,8 @@
           <t>hanako@example.co.jp</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>8:30</t>
-        </is>
+      <c r="C3" s="3" t="n">
+        <v>0.3541666666666667</v>
       </c>
       <c r="D3" s="4">
         <f>IF(N(C3)=0,"",C3+TIME(13,0,0))</f>
@@ -2909,7 +2905,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -2931,7 +2926,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -2939,7 +2933,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>

--- a/attendance-mail/勤務時間管理.xlsx
+++ b/attendance-mail/勤務時間管理.xlsx
@@ -2819,7 +2819,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>【勤務時間】13時間到達まで残り{remain}です</t>
+          <t>【安全のお知らせ】本日の13時間到達時刻は {limit} です</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2885,7 +2885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -2908,35 +2908,105 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>本日の出勤打刻は {in} です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>13時間に到達する時刻は {limit} です。</t>
+          <t>本日もお疲れさまです。安全運行のための時間のお知らせです。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13時間まで残り {remain} です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>退勤打刻を {limit} までに済ませてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>※本メールは自動送信です。</t>
+          <t xml:space="preserve">　出勤打刻　　　{in}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　13時間到達　　{limit}（残り {remain}）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>{limit} を目安に退勤できるよう、無理のない範囲でご調整ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>※このメールは、急いでいただくためのものではありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　運転中は絶対に確認せず、安全な場所に停車してからご覧ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　速度超過や無理な進路変更は、絶対にしないでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　時間に間に合わせることより、安全に帰ってくることが最優先です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>業務の都合でどうしても {limit} を超えそうなときは、</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>わかった時点で早めに配車担当までご連絡ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>超過は皆さん個人の責任ではなく、会社が調整すべきことです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>人員に余裕がなく、ご負担をおかけしている点は承知しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>連絡いただければ、こちらで対応を考えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>本日もありがとうございます。気をつけてお帰りください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>※本メールは自動送信です。返信は不要です。</t>
         </is>
       </c>
     </row>

--- a/attendance-mail/勤務時間管理.xlsx
+++ b/attendance-mail/勤務時間管理.xlsx
@@ -2901,115 +2901,68 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>{name} さん</t>
-        </is>
-      </c>
-    </row>
+          <t>{name} さん　お疲れさまです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>本日もお疲れさまです。安全運行のための時間のお知らせです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　出勤打刻　　　{in}</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">　出勤打刻　　{in}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　13時間到達　{limit}（残り {remain}）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　13時間到達　　{limit}（残り {remain}）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>{limit} を目安に退勤できるよう、無理のない範囲でご調整ください。</t>
+          <t>{limit} を目安に、無理のない範囲でご調整ください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>超えそうなときは早めに配車担当へご連絡ください。会社側で調整します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>※運転中は見ないでください。急ぐ必要はありません。安全が最優先です。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>※このメールは、急いでいただくためのものではありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　運転中は絶対に確認せず、安全な場所に停車してからご覧ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　速度超過や無理な進路変更は、絶対にしないでください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　時間に間に合わせることより、安全に帰ってくることが最優先です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>業務の都合でどうしても {limit} を超えそうなときは、</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>わかった時点で早めに配車担当までご連絡ください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>超過は皆さん個人の責任ではなく、会社が調整すべきことです。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>人員に余裕がなく、ご負担をおかけしている点は承知しています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>連絡いただければ、こちらで対応を考えます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>本日もありがとうございます。気をつけてお帰りください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>※本メールは自動送信です。返信は不要です。</t>
-        </is>
-      </c>
-    </row>
+          <t>※自動送信のため返信は不要です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
